--- a/results/광명금속/광명금속_valid_hybrid_CNN_with_LSTM_(36,32)_first_window.xlsx
+++ b/results/광명금속/광명금속_valid_hybrid_CNN_with_LSTM_(36,32)_first_window.xlsx
@@ -462,10 +462,10 @@
         <v>30.54</v>
       </c>
       <c r="C2" t="n">
-        <v>30.53999900817871</v>
+        <v>30.53999710083008</v>
       </c>
       <c r="D2" t="n">
-        <v>28.2283821105957</v>
+        <v>18.7258186340332</v>
       </c>
     </row>
     <row r="3">
@@ -476,10 +476,10 @@
         <v>31.44</v>
       </c>
       <c r="C3" t="n">
-        <v>31.44000053405762</v>
+        <v>31.44000244140625</v>
       </c>
       <c r="D3" t="n">
-        <v>27.19597244262695</v>
+        <v>20.76539993286133</v>
       </c>
     </row>
     <row r="4">
@@ -490,10 +490,10 @@
         <v>29.18</v>
       </c>
       <c r="C4" t="n">
-        <v>29.18000030517578</v>
+        <v>29.17999649047852</v>
       </c>
       <c r="D4" t="n">
-        <v>27.19325828552246</v>
+        <v>21.29930114746094</v>
       </c>
     </row>
     <row r="5">
@@ -507,7 +507,7 @@
         <v>26.52000045776367</v>
       </c>
       <c r="D5" t="n">
-        <v>26.46635818481445</v>
+        <v>22.28450965881348</v>
       </c>
     </row>
     <row r="6">
@@ -518,10 +518,10 @@
         <v>26.72</v>
       </c>
       <c r="C6" t="n">
-        <v>26.72000122070312</v>
+        <v>26.71999549865723</v>
       </c>
       <c r="D6" t="n">
-        <v>26.74771308898926</v>
+        <v>22.24271583557129</v>
       </c>
     </row>
     <row r="7">
@@ -532,10 +532,10 @@
         <v>26.58</v>
       </c>
       <c r="C7" t="n">
-        <v>26.57999992370605</v>
+        <v>26.57999610900879</v>
       </c>
       <c r="D7" t="n">
-        <v>25.98588371276855</v>
+        <v>22.68599891662598</v>
       </c>
     </row>
     <row r="8">
@@ -546,10 +546,10 @@
         <v>30.44</v>
       </c>
       <c r="C8" t="n">
-        <v>30.44000053405762</v>
+        <v>30.44000244140625</v>
       </c>
       <c r="D8" t="n">
-        <v>26.29216194152832</v>
+        <v>22.97176170349121</v>
       </c>
     </row>
     <row r="9">
@@ -563,7 +563,7 @@
         <v>31.97999954223633</v>
       </c>
       <c r="D9" t="n">
-        <v>27.19278144836426</v>
+        <v>24.33668327331543</v>
       </c>
     </row>
     <row r="10">
@@ -577,7 +577,7 @@
         <v>33.56000137329102</v>
       </c>
       <c r="D10" t="n">
-        <v>27.54771041870117</v>
+        <v>21.39027786254883</v>
       </c>
     </row>
     <row r="11">
@@ -591,7 +591,7 @@
         <v>32.43999862670898</v>
       </c>
       <c r="D11" t="n">
-        <v>27.10739135742188</v>
+        <v>20.27083778381348</v>
       </c>
     </row>
     <row r="12">
@@ -602,10 +602,10 @@
         <v>33.62</v>
       </c>
       <c r="C12" t="n">
-        <v>33.61999893188477</v>
+        <v>33.6199951171875</v>
       </c>
       <c r="D12" t="n">
-        <v>25.67647933959961</v>
+        <v>19.99239730834961</v>
       </c>
     </row>
     <row r="13">
@@ -619,7 +619,7 @@
         <v>30.93999862670898</v>
       </c>
       <c r="D13" t="n">
-        <v>22.79489517211914</v>
+        <v>17.13082885742188</v>
       </c>
     </row>
     <row r="14">
@@ -630,10 +630,10 @@
         <v>25.62</v>
       </c>
       <c r="C14" t="n">
-        <v>25.61999893188477</v>
+        <v>25.61999702453613</v>
       </c>
       <c r="D14" t="n">
-        <v>17.07938194274902</v>
+        <v>16.93559265136719</v>
       </c>
     </row>
     <row r="15">
@@ -647,7 +647,7 @@
         <v>6.139999866485596</v>
       </c>
       <c r="D15" t="n">
-        <v>11.85139656066895</v>
+        <v>15.12629318237305</v>
       </c>
     </row>
     <row r="16">
@@ -661,7 +661,7 @@
         <v>5.519999980926514</v>
       </c>
       <c r="D16" t="n">
-        <v>8.151498794555664</v>
+        <v>15.24953079223633</v>
       </c>
     </row>
     <row r="17">
@@ -675,7 +675,7 @@
         <v>5.659999847412109</v>
       </c>
       <c r="D17" t="n">
-        <v>9.455336570739746</v>
+        <v>14.86583423614502</v>
       </c>
     </row>
     <row r="18">
@@ -689,7 +689,7 @@
         <v>7.800000190734863</v>
       </c>
       <c r="D18" t="n">
-        <v>12.94533634185791</v>
+        <v>14.42629051208496</v>
       </c>
     </row>
     <row r="19">
@@ -700,10 +700,10 @@
         <v>23.66</v>
       </c>
       <c r="C19" t="n">
-        <v>23.65999984741211</v>
+        <v>23.65999603271484</v>
       </c>
       <c r="D19" t="n">
-        <v>18.66044044494629</v>
+        <v>15.76683235168457</v>
       </c>
     </row>
     <row r="20">
@@ -717,7 +717,7 @@
         <v>24.47999954223633</v>
       </c>
       <c r="D20" t="n">
-        <v>22.78197288513184</v>
+        <v>17.28535652160645</v>
       </c>
     </row>
     <row r="21">
@@ -728,10 +728,10 @@
         <v>25.3</v>
       </c>
       <c r="C21" t="n">
-        <v>25.30000114440918</v>
+        <v>25.29999923706055</v>
       </c>
       <c r="D21" t="n">
-        <v>25.65723991394043</v>
+        <v>19.84239196777344</v>
       </c>
     </row>
     <row r="22">
@@ -742,10 +742,10 @@
         <v>25.06</v>
       </c>
       <c r="C22" t="n">
-        <v>25.05999946594238</v>
+        <v>25.05999755859375</v>
       </c>
       <c r="D22" t="n">
-        <v>26.08850479125977</v>
+        <v>19.94116020202637</v>
       </c>
     </row>
     <row r="23">
@@ -756,10 +756,10 @@
         <v>32.52</v>
       </c>
       <c r="C23" t="n">
-        <v>32.52000045776367</v>
+        <v>32.51999664306641</v>
       </c>
       <c r="D23" t="n">
-        <v>25.24879837036133</v>
+        <v>22.16760635375977</v>
       </c>
     </row>
     <row r="24">
@@ -770,10 +770,10 @@
         <v>26.24</v>
       </c>
       <c r="C24" t="n">
-        <v>26.23999977111816</v>
+        <v>26.2399959564209</v>
       </c>
       <c r="D24" t="n">
-        <v>24.78866958618164</v>
+        <v>20.06991767883301</v>
       </c>
     </row>
     <row r="25">
@@ -784,10 +784,10 @@
         <v>25.66</v>
       </c>
       <c r="C25" t="n">
-        <v>25.65999984741211</v>
+        <v>25.65999794006348</v>
       </c>
       <c r="D25" t="n">
-        <v>23.78968811035156</v>
+        <v>20.44287109375</v>
       </c>
     </row>
     <row r="26">
@@ -801,7 +801,7 @@
         <v>21.05999946594238</v>
       </c>
       <c r="D26" t="n">
-        <v>23.30291366577148</v>
+        <v>22.93169593811035</v>
       </c>
     </row>
     <row r="27">
@@ -812,10 +812,10 @@
         <v>18.38</v>
       </c>
       <c r="C27" t="n">
-        <v>18.3799991607666</v>
+        <v>18.37999725341797</v>
       </c>
       <c r="D27" t="n">
-        <v>23.08274459838867</v>
+        <v>24.48892593383789</v>
       </c>
     </row>
     <row r="28">
@@ -829,7 +829,7 @@
         <v>18.11999893188477</v>
       </c>
       <c r="D28" t="n">
-        <v>23.58345985412598</v>
+        <v>24.02877044677734</v>
       </c>
     </row>
     <row r="29">
@@ -840,10 +840,10 @@
         <v>18.6</v>
       </c>
       <c r="C29" t="n">
-        <v>18.60000038146973</v>
+        <v>18.59999656677246</v>
       </c>
       <c r="D29" t="n">
-        <v>22.12371063232422</v>
+        <v>27.07274055480957</v>
       </c>
     </row>
     <row r="30">
@@ -857,7 +857,7 @@
         <v>18.11999893188477</v>
       </c>
       <c r="D30" t="n">
-        <v>21.93801307678223</v>
+        <v>25.65371322631836</v>
       </c>
     </row>
     <row r="31">
@@ -868,10 +868,10 @@
         <v>18.32</v>
       </c>
       <c r="C31" t="n">
-        <v>18.31999969482422</v>
+        <v>18.32000160217285</v>
       </c>
       <c r="D31" t="n">
-        <v>22.84395980834961</v>
+        <v>24.01473999023438</v>
       </c>
     </row>
     <row r="32">
@@ -882,10 +882,10 @@
         <v>18.42</v>
       </c>
       <c r="C32" t="n">
-        <v>18.42000007629395</v>
+        <v>18.41999816894531</v>
       </c>
       <c r="D32" t="n">
-        <v>22.85708618164062</v>
+        <v>24.79295921325684</v>
       </c>
     </row>
     <row r="33">
@@ -899,7 +899,7 @@
         <v>21.13999938964844</v>
       </c>
       <c r="D33" t="n">
-        <v>22.63187980651855</v>
+        <v>21.80111885070801</v>
       </c>
     </row>
   </sheetData>
